--- a/public/samples/spws/filler.xlsx
+++ b/public/samples/spws/filler.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/kho SPW/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B47AC5-B9DA-3042-82C9-30C1E6A6B0E2}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{41CC62C9-A87E-5545-B8D9-1420143DBFF3}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
   <si>
     <t>Tồn</t>
   </si>
@@ -58,6 +47,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>F G 025</t>
@@ -165,29 +157,370 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -195,27 +528,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -264,7 +883,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -297,26 +916,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -349,23 +951,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -507,21 +1092,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B93133F-5468-3A41-9D1A-BE5FE45154BD}">
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:11">
       <c r="C1" s="1"/>
       <c r="G1" s="2"/>
       <c r="J1" s="3"/>
@@ -529,7 +1109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -566,13 +1146,16 @@
       <c r="L2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>2.5</v>
@@ -587,10 +1170,10 @@
         <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3">
@@ -600,12 +1183,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
         <v>3.2</v>
@@ -620,25 +1203,25 @@
         <v>63</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4" s="2">
-        <v>25.200000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>4.5</v>
@@ -653,10 +1236,10 @@
         <v>527</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5">
@@ -666,12 +1249,12 @@
         <v>390.6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>4.5</v>
@@ -683,13 +1266,13 @@
         <v>156</v>
       </c>
       <c r="G6" s="2">
-        <v>1029.5999999999999</v>
+        <v>1029.6</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6">
@@ -699,12 +1282,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>6.4</v>
@@ -716,28 +1299,28 @@
         <v>19</v>
       </c>
       <c r="G7" s="2">
-        <v>125.39999999999999</v>
+        <v>125.4</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7">
         <v>19</v>
       </c>
       <c r="L7" s="2">
-        <v>125.39999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+        <v>125.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>3.2</v>
@@ -749,13 +1332,13 @@
         <v>17</v>
       </c>
       <c r="G8" s="2">
-        <v>6.8000000000000007</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8">
@@ -765,12 +1348,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>4.5</v>
@@ -785,10 +1368,10 @@
         <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9">
@@ -798,12 +1381,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>4.5</v>
@@ -818,10 +1401,10 @@
         <v>53.6</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10">
@@ -831,12 +1414,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1">
         <v>4.5</v>
@@ -851,10 +1434,10 @@
         <v>63.8</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11">
@@ -864,12 +1447,12 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>2.5</v>
@@ -881,28 +1464,28 @@
         <v>6</v>
       </c>
       <c r="G12" s="2">
-        <v>14.399999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" s="2">
-        <v>14.399999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="1">
         <v>3.2</v>
@@ -914,28 +1497,28 @@
         <v>3</v>
       </c>
       <c r="G13" s="2">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13">
         <v>3</v>
       </c>
       <c r="L13" s="2">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1">
         <v>4.5</v>
@@ -950,10 +1533,10 @@
         <v>7.4</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14">
@@ -963,12 +1546,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
         <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
       </c>
       <c r="C15" s="1">
         <v>4.5</v>
@@ -983,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15">
         <v>2100001</v>
@@ -998,12 +1581,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>4.5</v>
@@ -1018,7 +1601,7 @@
         <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16">
         <v>2100001</v>
@@ -1033,12 +1616,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1">
         <v>4.5</v>
@@ -1050,13 +1633,13 @@
         <v>14</v>
       </c>
       <c r="G17" s="2">
-        <v>51.800000000000004</v>
+        <v>51.8</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3">
         <v>44604</v>
@@ -1065,15 +1648,15 @@
         <v>3</v>
       </c>
       <c r="L17" s="2">
-        <v>11.099999999999994</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1">
         <v>4.5</v>
@@ -1088,10 +1671,10 @@
         <v>100.5</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="3">
         <v>44604</v>
@@ -1103,12 +1686,12 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1">
         <v>4.5</v>
@@ -1123,10 +1706,10 @@
         <v>980</v>
       </c>
       <c r="H19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="3">
         <v>44708</v>
@@ -1138,12 +1721,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1">
         <v>6.4</v>
@@ -1155,13 +1738,13 @@
         <v>17</v>
       </c>
       <c r="G20" s="2">
-        <v>120.69999999999999</v>
+        <v>120.7</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3">
         <v>44708</v>
@@ -1170,15 +1753,15 @@
         <v>17</v>
       </c>
       <c r="L20" s="2">
-        <v>120.69999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+        <v>120.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1">
         <v>4.5</v>
@@ -1193,10 +1776,10 @@
         <v>496</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" s="3">
         <v>44868</v>
@@ -1208,12 +1791,12 @@
         <v>496</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1">
         <v>4.5</v>
@@ -1225,13 +1808,13 @@
         <v>227</v>
       </c>
       <c r="G22" s="2">
-        <v>1498.1999999999998</v>
+        <v>1498.2</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3">
         <v>44868</v>
@@ -1240,21 +1823,21 @@
         <v>227</v>
       </c>
       <c r="L22" s="2">
-        <v>1498.1999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1498.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1">
         <v>3.2</v>
       </c>
       <c r="D23">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -1263,10 +1846,10 @@
         <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3">
         <v>44887</v>
@@ -1278,12 +1861,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
         <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
       </c>
       <c r="C24" s="1">
         <v>4.5</v>
@@ -1298,10 +1881,10 @@
         <v>203</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J24" s="3">
         <v>44887</v>
@@ -1313,12 +1896,12 @@
         <v>197.2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="1">
         <v>25.4</v>
@@ -1333,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J25" s="3">
         <v>44887</v>
@@ -1348,15 +1931,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" s="1">
-        <v>19.100000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="E26">
         <v>15</v>
@@ -1368,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J26" s="3">
         <v>44887</v>
@@ -1383,12 +1966,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1403,10 +1986,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="3">
         <v>44887</v>
@@ -1420,5 +2003,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>